--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MINNESOTA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MINNESOTA_2016.xlsx
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C220">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 26-</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C596">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C625">
